--- a/artfynd/A 39258-2024 artfynd.xlsx
+++ b/artfynd/A 39258-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120443740</v>
+        <v>120443966</v>
       </c>
       <c r="B2" t="n">
-        <v>90600</v>
+        <v>91881</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591866</v>
+        <v>591672</v>
       </c>
       <c r="R2" t="n">
-        <v>6391259</v>
+        <v>6391524</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120443979</v>
+        <v>120443402</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>94704</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,34 +805,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591864</v>
+        <v>591739</v>
       </c>
       <c r="R3" t="n">
-        <v>6391341</v>
+        <v>6391467</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,17 +889,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120443691</v>
+        <v>120443740</v>
       </c>
       <c r="B4" t="n">
-        <v>91881</v>
+        <v>90600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,26 +912,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -950,14 +943,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 39258, Sm</t>
+          <t>A 39258, Mörhult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591821</v>
+        <v>591866</v>
       </c>
       <c r="R4" t="n">
-        <v>6391385</v>
+        <v>6391259</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120443402</v>
+        <v>120443691</v>
       </c>
       <c r="B5" t="n">
-        <v>94704</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,42 +1022,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 39258, Mörhult, Sm</t>
+          <t>A 39258, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591739</v>
+        <v>591821</v>
       </c>
       <c r="R5" t="n">
-        <v>6391467</v>
+        <v>6391385</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120443966</v>
+        <v>120443979</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,30 +1136,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591672</v>
+        <v>591864</v>
       </c>
       <c r="R6" t="n">
-        <v>6391524</v>
+        <v>6391341</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 39258-2024 artfynd.xlsx
+++ b/artfynd/A 39258-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120443966</v>
+        <v>120443402</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591672</v>
+        <v>591739</v>
       </c>
       <c r="R2" t="n">
-        <v>6391524</v>
+        <v>6391467</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120443402</v>
+        <v>120443966</v>
       </c>
       <c r="B3" t="n">
-        <v>94704</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,31 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591739</v>
+        <v>591672</v>
       </c>
       <c r="R3" t="n">
-        <v>6391467</v>
+        <v>6391524</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,17 +889,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120443740</v>
+        <v>120443979</v>
       </c>
       <c r="B4" t="n">
-        <v>90600</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,25 +908,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591866</v>
+        <v>591864</v>
       </c>
       <c r="R4" t="n">
-        <v>6391259</v>
+        <v>6391341</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120443979</v>
+        <v>120443740</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>90600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,25 +1136,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591864</v>
+        <v>591866</v>
       </c>
       <c r="R6" t="n">
-        <v>6391341</v>
+        <v>6391259</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 39258-2024 artfynd.xlsx
+++ b/artfynd/A 39258-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120443402</v>
+        <v>120443966</v>
       </c>
       <c r="B2" t="n">
-        <v>94704</v>
+        <v>91881</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591739</v>
+        <v>591672</v>
       </c>
       <c r="R2" t="n">
-        <v>6391467</v>
+        <v>6391524</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120443966</v>
+        <v>120443979</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,30 +801,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -833,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591672</v>
+        <v>591864</v>
       </c>
       <c r="R3" t="n">
-        <v>6391524</v>
+        <v>6391341</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120443979</v>
+        <v>120443402</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>94704</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,34 +919,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591864</v>
+        <v>591739</v>
       </c>
       <c r="R4" t="n">
-        <v>6391341</v>
+        <v>6391467</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120443691</v>
+        <v>120443740</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>90600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,26 +1026,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,14 +1057,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 39258, Sm</t>
+          <t>A 39258, Mörhult, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591821</v>
+        <v>591866</v>
       </c>
       <c r="R5" t="n">
-        <v>6391385</v>
+        <v>6391259</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120443740</v>
+        <v>120443691</v>
       </c>
       <c r="B6" t="n">
-        <v>90600</v>
+        <v>91881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,26 +1140,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1171,14 +1171,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 39258, Mörhult, Sm</t>
+          <t>A 39258, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591866</v>
+        <v>591821</v>
       </c>
       <c r="R6" t="n">
-        <v>6391259</v>
+        <v>6391385</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 39258-2024 artfynd.xlsx
+++ b/artfynd/A 39258-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120443966</v>
+        <v>120443402</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>94704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591672</v>
+        <v>591739</v>
       </c>
       <c r="R2" t="n">
-        <v>6391524</v>
+        <v>6391467</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120443979</v>
+        <v>120443966</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,30 +794,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -840,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591864</v>
+        <v>591672</v>
       </c>
       <c r="R3" t="n">
-        <v>6391341</v>
+        <v>6391524</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120443402</v>
+        <v>120443740</v>
       </c>
       <c r="B4" t="n">
-        <v>94704</v>
+        <v>90600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,31 +908,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591739</v>
+        <v>591866</v>
       </c>
       <c r="R4" t="n">
-        <v>6391467</v>
+        <v>6391259</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120443740</v>
+        <v>120443691</v>
       </c>
       <c r="B5" t="n">
-        <v>90600</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,26 +1026,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,14 +1057,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 39258, Mörhult, Sm</t>
+          <t>A 39258, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591866</v>
+        <v>591821</v>
       </c>
       <c r="R5" t="n">
-        <v>6391259</v>
+        <v>6391385</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120443691</v>
+        <v>120443979</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,30 +1136,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1171,14 +1171,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 39258, Sm</t>
+          <t>A 39258, Mörhult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591821</v>
+        <v>591864</v>
       </c>
       <c r="R6" t="n">
-        <v>6391385</v>
+        <v>6391341</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
